--- a/WorkBot/refactor-experimental/data/orders/BALKAN BEVERAGE LLC/BALKAN BEVERAGE LLC_Collegetown_20251114.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/BALKAN BEVERAGE LLC/BALKAN BEVERAGE LLC_Collegetown_20251114.xlsx
@@ -454,20 +454,14 @@
           <t>Vita Coco - Coconut Water 500ml</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>53.00</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>106.00</t>
-        </is>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>53</v>
+      </c>
+      <c r="E2" t="n">
+        <v>106</v>
       </c>
     </row>
     <row r="3">
@@ -481,20 +475,14 @@
           <t>Vita Coco - Coconut Water 1L</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>53.00</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>53.00</t>
-        </is>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>53</v>
+      </c>
+      <c r="E3" t="n">
+        <v>53</v>
       </c>
     </row>
     <row r="4">
@@ -508,20 +496,14 @@
           <t>Red Bull</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>42.85</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>85.70</t>
-        </is>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>42.85</v>
+      </c>
+      <c r="E4" t="n">
+        <v>85.7</v>
       </c>
     </row>
     <row r="5">
@@ -535,20 +517,14 @@
           <t>Red Bull - Yellow</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>42.85</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>42.85</t>
-        </is>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>42.85</v>
+      </c>
+      <c r="E5" t="n">
+        <v>42.85</v>
       </c>
     </row>
   </sheetData>

--- a/WorkBot/refactor-experimental/data/orders/BALKAN BEVERAGE LLC/BALKAN BEVERAGE LLC_Collegetown_20251114.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/BALKAN BEVERAGE LLC/BALKAN BEVERAGE LLC_Collegetown_20251114.xlsx
@@ -455,13 +455,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
         <v>53</v>
       </c>
       <c r="E2" t="n">
-        <v>106</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3">
@@ -476,13 +476,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
         <v>53</v>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
         <v>42.85</v>
       </c>
       <c r="E4" t="n">
-        <v>85.7</v>
+        <v>128.55</v>
       </c>
     </row>
     <row r="5">
@@ -518,13 +518,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
         <v>42.85</v>
       </c>
       <c r="E5" t="n">
-        <v>42.85</v>
+        <v>85.7</v>
       </c>
     </row>
   </sheetData>
